--- a/WTO_Database.xlsx
+++ b/WTO_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Streamlit Github WTO Database\WTO TRCM Database for TL101\WTO App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C646C9-4332-470C-BABE-9CFA73F77407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4DE0EA-E376-4A44-8A1E-EDAF1529C139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7500" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Database!$A$1:$Y$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Database!$A$1:$Y$230</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Governance Dimension_Topics'!$B$2:$E$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="437">
   <si>
     <t>Document_Symbol</t>
   </si>
@@ -926,9 +926,6 @@
     <t>11.4–11.14</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>11.16–11.17</t>
   </si>
   <si>
@@ -1341,9 +1338,6 @@
   </si>
   <si>
     <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>National &amp; Economic Security</t>
   </si>
   <si>
     <t>9.26-9.29</t>
@@ -2020,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y229"/>
+  <dimension ref="A1:Y230"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -7843,7 +7837,7 @@
         <v>233</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>234</v>
@@ -9539,13 +9533,11 @@
       <c r="G126" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H126" s="9"/>
+      <c r="H126" s="25"/>
       <c r="I126" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="J126" s="9" t="s">
-        <v>96</v>
-      </c>
+      <c r="J126" s="9"/>
       <c r="K126" s="9"/>
       <c r="L126" s="9" t="s">
         <v>284</v>
@@ -9992,7 +9984,7 @@
         <v>215</v>
       </c>
       <c r="H133" s="23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I133" s="23" t="s">
         <v>231</v>
@@ -10058,7 +10050,7 @@
         <v>215</v>
       </c>
       <c r="H134" s="23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I134" s="23" t="s">
         <v>231</v>
@@ -10124,7 +10116,7 @@
         <v>215</v>
       </c>
       <c r="H135" s="23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I135" s="23" t="s">
         <v>231</v>
@@ -10180,7 +10172,7 @@
         <v>215</v>
       </c>
       <c r="H136" s="23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I136" s="23" t="s">
         <v>231</v>
@@ -10237,7 +10229,7 @@
         <v>277</v>
       </c>
       <c r="E137" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F137" s="23" t="s">
         <v>25</v>
@@ -10246,7 +10238,7 @@
         <v>215</v>
       </c>
       <c r="H137" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I137" s="23" t="s">
         <v>231</v>
@@ -10298,7 +10290,7 @@
         <v>277</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F138" s="23" t="s">
         <v>34</v>
@@ -10307,7 +10299,7 @@
         <v>215</v>
       </c>
       <c r="H138" s="23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I138" s="23" t="s">
         <v>231</v>
@@ -10385,7 +10377,7 @@
         <v>215</v>
       </c>
       <c r="H139" s="23" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I139" s="23" t="s">
         <v>231</v>
@@ -10453,7 +10445,7 @@
         <v>215</v>
       </c>
       <c r="H140" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I140" s="23" t="s">
         <v>231</v>
@@ -10510,7 +10502,7 @@
         <v>277</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F141" s="23" t="s">
         <v>55</v>
@@ -10519,7 +10511,7 @@
         <v>215</v>
       </c>
       <c r="H141" s="23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I141" s="23" t="s">
         <v>231</v>
@@ -10583,7 +10575,7 @@
         <v>277</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F142" s="23" t="s">
         <v>34</v>
@@ -10592,7 +10584,7 @@
         <v>215</v>
       </c>
       <c r="H142" s="23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I142" s="23" t="s">
         <v>231</v>
@@ -10659,7 +10651,7 @@
         <v>277</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F143" s="23" t="s">
         <v>34</v>
@@ -10668,7 +10660,7 @@
         <v>215</v>
       </c>
       <c r="H143" s="23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I143" s="23" t="s">
         <v>231</v>
@@ -10730,7 +10722,7 @@
         <v>277</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F144" s="23" t="s">
         <v>34</v>
@@ -10739,7 +10731,7 @@
         <v>215</v>
       </c>
       <c r="H144" s="23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I144" s="23" t="s">
         <v>231</v>
@@ -10796,7 +10788,7 @@
         <v>277</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F145" s="23" t="s">
         <v>34</v>
@@ -10805,7 +10797,7 @@
         <v>215</v>
       </c>
       <c r="H145" s="23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I145" s="23" t="s">
         <v>231</v>
@@ -10876,7 +10868,7 @@
         <v>215</v>
       </c>
       <c r="H146" s="23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I146" s="23" t="s">
         <v>231</v>
@@ -10947,7 +10939,7 @@
         <v>215</v>
       </c>
       <c r="H147" s="23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I147" s="23" t="s">
         <v>231</v>
@@ -11018,7 +11010,7 @@
         <v>215</v>
       </c>
       <c r="H148" s="23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I148" s="23" t="s">
         <v>231</v>
@@ -11080,7 +11072,7 @@
         <v>277</v>
       </c>
       <c r="E149" s="23" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F149" s="23" t="s">
         <v>34</v>
@@ -11089,7 +11081,7 @@
         <v>215</v>
       </c>
       <c r="H149" s="23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I149" s="23" t="s">
         <v>231</v>
@@ -11160,7 +11152,7 @@
         <v>215</v>
       </c>
       <c r="H150" s="23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I150" s="23" t="s">
         <v>231</v>
@@ -11212,7 +11204,7 @@
         <v>277</v>
       </c>
       <c r="E151" s="23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F151" s="23" t="s">
         <v>34</v>
@@ -11221,7 +11213,7 @@
         <v>215</v>
       </c>
       <c r="H151" s="23" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I151" s="23" t="s">
         <v>231</v>
@@ -11292,7 +11284,7 @@
         <v>215</v>
       </c>
       <c r="H152" s="23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I152" s="23" t="s">
         <v>231</v>
@@ -11354,7 +11346,7 @@
         <v>277</v>
       </c>
       <c r="E153" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F153" s="23" t="s">
         <v>34</v>
@@ -11363,7 +11355,7 @@
         <v>215</v>
       </c>
       <c r="H153" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I153" s="23" t="s">
         <v>231</v>
@@ -11430,7 +11422,7 @@
         <v>277</v>
       </c>
       <c r="E154" s="23" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F154" s="23" t="s">
         <v>34</v>
@@ -11439,7 +11431,7 @@
         <v>215</v>
       </c>
       <c r="H154" s="23" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I154" s="23" t="s">
         <v>231</v>
@@ -11510,7 +11502,7 @@
         <v>215</v>
       </c>
       <c r="H155" s="23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I155" s="23" t="s">
         <v>231</v>
@@ -11581,7 +11573,7 @@
         <v>215</v>
       </c>
       <c r="H156" s="23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I156" s="23" t="s">
         <v>231</v>
@@ -11638,7 +11630,7 @@
         <v>277</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F157" s="23" t="s">
         <v>34</v>
@@ -11647,7 +11639,7 @@
         <v>215</v>
       </c>
       <c r="H157" s="23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I157" s="23" t="s">
         <v>231</v>
@@ -11714,7 +11706,7 @@
         <v>277</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F158" s="23" t="s">
         <v>34</v>
@@ -11723,7 +11715,7 @@
         <v>215</v>
       </c>
       <c r="H158" s="23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I158" s="23" t="s">
         <v>231</v>
@@ -11794,7 +11786,7 @@
         <v>215</v>
       </c>
       <c r="H159" s="23" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I159" s="23" t="s">
         <v>231</v>
@@ -11865,7 +11857,7 @@
         <v>215</v>
       </c>
       <c r="H160" s="23" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I160" s="23" t="s">
         <v>231</v>
@@ -11927,7 +11919,7 @@
         <v>277</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F161" s="23" t="s">
         <v>34</v>
@@ -11936,7 +11928,7 @@
         <v>215</v>
       </c>
       <c r="H161" s="23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I161" s="23" t="s">
         <v>231</v>
@@ -11998,7 +11990,7 @@
         <v>277</v>
       </c>
       <c r="E162" s="23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F162" s="23" t="s">
         <v>34</v>
@@ -12007,7 +11999,7 @@
         <v>215</v>
       </c>
       <c r="H162" s="23" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I162" s="23" t="s">
         <v>231</v>
@@ -12078,7 +12070,7 @@
         <v>215</v>
       </c>
       <c r="H163" s="23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I163" s="23" t="s">
         <v>231</v>
@@ -12135,7 +12127,7 @@
         <v>277</v>
       </c>
       <c r="E164" s="23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F164" s="23" t="s">
         <v>34</v>
@@ -12144,7 +12136,7 @@
         <v>215</v>
       </c>
       <c r="H164" s="23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I164" s="23" t="s">
         <v>231</v>
@@ -12206,7 +12198,7 @@
         <v>277</v>
       </c>
       <c r="E165" s="23" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F165" s="23" t="s">
         <v>34</v>
@@ -12215,7 +12207,7 @@
         <v>215</v>
       </c>
       <c r="H165" s="23" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I165" s="23" t="s">
         <v>231</v>
@@ -12286,7 +12278,7 @@
         <v>215</v>
       </c>
       <c r="H166" s="23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I166" s="23" t="s">
         <v>231</v>
@@ -12352,7 +12344,7 @@
         <v>215</v>
       </c>
       <c r="H167" s="23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I167" s="23" t="s">
         <v>231</v>
@@ -12413,7 +12405,7 @@
         <v>215</v>
       </c>
       <c r="H168" s="23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I168" s="23" t="s">
         <v>231</v>
@@ -12484,7 +12476,7 @@
         <v>215</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I169" s="9" t="s">
         <v>231</v>
@@ -12551,7 +12543,7 @@
         <v>277</v>
       </c>
       <c r="E170" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>34</v>
@@ -12560,7 +12552,7 @@
         <v>215</v>
       </c>
       <c r="H170" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I170" s="9" t="s">
         <v>231</v>
@@ -12622,7 +12614,7 @@
         <v>277</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>34</v>
@@ -12631,7 +12623,7 @@
         <v>215</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I171" s="9" t="s">
         <v>231</v>
@@ -12697,7 +12689,7 @@
         <v>215</v>
       </c>
       <c r="H172" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I172" s="9" t="s">
         <v>231</v>
@@ -12773,7 +12765,7 @@
         <v>215</v>
       </c>
       <c r="H173" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I173" s="9" t="s">
         <v>231</v>
@@ -12830,7 +12822,7 @@
         <v>277</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>34</v>
@@ -12839,7 +12831,7 @@
         <v>215</v>
       </c>
       <c r="H174" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I174" s="9" t="s">
         <v>231</v>
@@ -12906,7 +12898,7 @@
         <v>277</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>34</v>
@@ -12915,7 +12907,7 @@
         <v>215</v>
       </c>
       <c r="H175" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I175" s="9" t="s">
         <v>231</v>
@@ -12972,7 +12964,7 @@
         <v>277</v>
       </c>
       <c r="E176" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>34</v>
@@ -12981,7 +12973,7 @@
         <v>215</v>
       </c>
       <c r="H176" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I176" s="9" t="s">
         <v>231</v>
@@ -13047,7 +13039,7 @@
         <v>215</v>
       </c>
       <c r="H177" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I177" s="9" t="s">
         <v>231</v>
@@ -13114,26 +13106,24 @@
         <v>277</v>
       </c>
       <c r="E178" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G178" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H178" s="9" t="s">
-        <v>363</v>
+        <v>26</v>
+      </c>
+      <c r="H178" s="25" t="s">
+        <v>362</v>
       </c>
       <c r="I178" s="9" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="J178" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="K178" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="K178" s="9"/>
       <c r="L178" s="9" t="s">
         <v>177</v>
       </c>
@@ -13193,7 +13183,7 @@
         <v>215</v>
       </c>
       <c r="H179" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I179" s="9" t="s">
         <v>231</v>
@@ -13256,10 +13246,10 @@
         <v>34</v>
       </c>
       <c r="G180" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H180" s="9" t="s">
-        <v>365</v>
+        <v>26</v>
+      </c>
+      <c r="H180" s="25" t="s">
+        <v>364</v>
       </c>
       <c r="I180" s="9" t="s">
         <v>242</v>
@@ -13267,9 +13257,7 @@
       <c r="J180" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="K180" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="K180" s="9"/>
       <c r="L180" s="9" t="s">
         <v>177</v>
       </c>
@@ -13339,17 +13327,13 @@
         <v>59</v>
       </c>
       <c r="H181" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I181" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J181" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K181" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J181" s="9"/>
+      <c r="K181" s="9"/>
       <c r="L181" s="9" t="s">
         <v>177</v>
       </c>
@@ -13409,17 +13393,13 @@
         <v>59</v>
       </c>
       <c r="H182" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I182" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J182" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K182" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J182" s="9"/>
+      <c r="K182" s="9"/>
       <c r="L182" s="9" t="s">
         <v>177</v>
       </c>
@@ -13470,7 +13450,7 @@
         <v>277</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>25</v>
@@ -13479,17 +13459,13 @@
         <v>59</v>
       </c>
       <c r="H183" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I183" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J183" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K183" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J183" s="9"/>
+      <c r="K183" s="9"/>
       <c r="L183" s="9" t="s">
         <v>177</v>
       </c>
@@ -13549,17 +13525,13 @@
         <v>59</v>
       </c>
       <c r="H184" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I184" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J184" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K184" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J184" s="9"/>
+      <c r="K184" s="9"/>
       <c r="L184" s="9" t="s">
         <v>177</v>
       </c>
@@ -13624,17 +13596,13 @@
         <v>59</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I185" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J185" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K185" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J185" s="9"/>
+      <c r="K185" s="9"/>
       <c r="L185" s="9" t="s">
         <v>177</v>
       </c>
@@ -13694,17 +13662,13 @@
         <v>59</v>
       </c>
       <c r="H186" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I186" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J186" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K186" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J186" s="9"/>
+      <c r="K186" s="9"/>
       <c r="L186" s="9" t="s">
         <v>177</v>
       </c>
@@ -13750,7 +13714,7 @@
         <v>277</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>34</v>
@@ -13759,17 +13723,13 @@
         <v>59</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I187" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J187" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K187" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J187" s="9"/>
+      <c r="K187" s="9"/>
       <c r="L187" s="9" t="s">
         <v>177</v>
       </c>
@@ -13839,17 +13799,13 @@
         <v>59</v>
       </c>
       <c r="H188" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I188" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J188" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K188" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J188" s="9"/>
+      <c r="K188" s="9"/>
       <c r="L188" s="9" t="s">
         <v>177</v>
       </c>
@@ -13909,17 +13865,13 @@
         <v>59</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I189" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J189" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K189" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J189" s="9"/>
+      <c r="K189" s="9"/>
       <c r="L189" s="9" t="s">
         <v>177</v>
       </c>
@@ -13989,17 +13941,13 @@
         <v>59</v>
       </c>
       <c r="H190" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I190" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J190" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K190" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J190" s="9"/>
+      <c r="K190" s="9"/>
       <c r="L190" s="9" t="s">
         <v>177</v>
       </c>
@@ -14069,17 +14017,13 @@
         <v>59</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I191" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J191" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K191" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J191" s="9"/>
+      <c r="K191" s="9"/>
       <c r="L191" s="9" t="s">
         <v>177</v>
       </c>
@@ -14149,17 +14093,13 @@
         <v>59</v>
       </c>
       <c r="H192" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I192" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J192" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K192" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J192" s="9"/>
+      <c r="K192" s="9"/>
       <c r="L192" s="9" t="s">
         <v>177</v>
       </c>
@@ -14205,7 +14145,7 @@
         <v>277</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>34</v>
@@ -14214,17 +14154,13 @@
         <v>59</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I193" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J193" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K193" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J193" s="9"/>
+      <c r="K193" s="9"/>
       <c r="L193" s="9" t="s">
         <v>177</v>
       </c>
@@ -14284,17 +14220,13 @@
         <v>59</v>
       </c>
       <c r="H194" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I194" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J194" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K194" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J194" s="9"/>
+      <c r="K194" s="9"/>
       <c r="L194" s="9" t="s">
         <v>177</v>
       </c>
@@ -14345,7 +14277,7 @@
         <v>277</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>34</v>
@@ -14354,17 +14286,13 @@
         <v>59</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I195" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J195" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K195" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J195" s="9"/>
+      <c r="K195" s="9"/>
       <c r="L195" s="9" t="s">
         <v>177</v>
       </c>
@@ -14434,17 +14362,13 @@
         <v>59</v>
       </c>
       <c r="H196" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I196" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J196" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K196" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J196" s="9"/>
+      <c r="K196" s="9"/>
       <c r="L196" s="9" t="s">
         <v>177</v>
       </c>
@@ -14505,7 +14429,7 @@
         <v>277</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>34</v>
@@ -14514,17 +14438,13 @@
         <v>59</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I197" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J197" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K197" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J197" s="9"/>
+      <c r="K197" s="9"/>
       <c r="L197" s="9" t="s">
         <v>177</v>
       </c>
@@ -14575,7 +14495,7 @@
         <v>277</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>34</v>
@@ -14584,17 +14504,13 @@
         <v>59</v>
       </c>
       <c r="H198" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I198" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J198" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K198" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J198" s="9"/>
+      <c r="K198" s="9"/>
       <c r="L198" s="9" t="s">
         <v>177</v>
       </c>
@@ -14649,17 +14565,13 @@
         <v>59</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I199" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J199" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K199" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J199" s="9"/>
+      <c r="K199" s="9"/>
       <c r="L199" s="9" t="s">
         <v>177</v>
       </c>
@@ -14729,17 +14641,13 @@
         <v>59</v>
       </c>
       <c r="H200" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I200" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J200" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K200" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
       <c r="L200" s="9" t="s">
         <v>177</v>
       </c>
@@ -14799,17 +14707,13 @@
         <v>59</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I201" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J201" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K201" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J201" s="9"/>
+      <c r="K201" s="9"/>
       <c r="L201" s="9" t="s">
         <v>177</v>
       </c>
@@ -14869,17 +14773,13 @@
         <v>59</v>
       </c>
       <c r="H202" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I202" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J202" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K202" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J202" s="9"/>
+      <c r="K202" s="9"/>
       <c r="L202" s="9" t="s">
         <v>177</v>
       </c>
@@ -14925,7 +14825,7 @@
         <v>277</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>34</v>
@@ -14934,17 +14834,13 @@
         <v>59</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I203" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J203" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K203" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J203" s="9"/>
+      <c r="K203" s="9"/>
       <c r="L203" s="9" t="s">
         <v>177</v>
       </c>
@@ -15014,17 +14910,13 @@
         <v>59</v>
       </c>
       <c r="H204" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I204" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J204" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K204" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J204" s="9"/>
+      <c r="K204" s="9"/>
       <c r="L204" s="9" t="s">
         <v>177</v>
       </c>
@@ -15079,17 +14971,13 @@
         <v>59</v>
       </c>
       <c r="H205" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I205" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J205" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K205" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J205" s="9"/>
+      <c r="K205" s="9"/>
       <c r="L205" s="9" t="s">
         <v>177</v>
       </c>
@@ -15149,17 +15037,13 @@
         <v>59</v>
       </c>
       <c r="H206" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I206" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J206" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K206" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J206" s="9"/>
+      <c r="K206" s="9"/>
       <c r="L206" s="9" t="s">
         <v>177</v>
       </c>
@@ -15215,7 +15099,7 @@
         <v>277</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>55</v>
@@ -15224,17 +15108,13 @@
         <v>59</v>
       </c>
       <c r="H207" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I207" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J207" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K207" s="9" t="s">
-        <v>294</v>
-      </c>
+      <c r="J207" s="9"/>
+      <c r="K207" s="9"/>
       <c r="L207" s="9" t="s">
         <v>177</v>
       </c>
@@ -15298,8 +15178,8 @@
       <c r="G208" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H208" s="9" t="s">
-        <v>397</v>
+      <c r="H208" s="25" t="s">
+        <v>396</v>
       </c>
       <c r="I208" s="9" t="s">
         <v>242</v>
@@ -15307,9 +15187,7 @@
       <c r="J208" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="K208" s="9" t="s">
-        <v>182</v>
-      </c>
+      <c r="K208" s="9"/>
       <c r="L208" s="9" t="s">
         <v>177</v>
       </c>
@@ -15379,7 +15257,7 @@
         <v>26</v>
       </c>
       <c r="H209" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I209" s="9" t="s">
         <v>135</v>
@@ -15390,8 +15268,8 @@
       <c r="K209" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="L209" s="25" t="s">
-        <v>438</v>
+      <c r="L209" s="9" t="s">
+        <v>436</v>
       </c>
       <c r="M209" s="9" t="s">
         <v>236</v>
@@ -15459,7 +15337,7 @@
         <v>26</v>
       </c>
       <c r="H210" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I210" s="9" t="s">
         <v>182</v>
@@ -15520,7 +15398,7 @@
         <v>26</v>
       </c>
       <c r="H211" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I211" s="9" t="s">
         <v>182</v>
@@ -15586,7 +15464,7 @@
         <v>26</v>
       </c>
       <c r="H212" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I212" s="9" t="s">
         <v>163</v>
@@ -15598,7 +15476,7 @@
         <v>182</v>
       </c>
       <c r="L212" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M212" s="9" t="s">
         <v>191</v>
@@ -15657,7 +15535,7 @@
         <v>277</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>25</v>
@@ -15666,7 +15544,7 @@
         <v>26</v>
       </c>
       <c r="H213" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I213" s="9" t="s">
         <v>163</v>
@@ -15675,8 +15553,8 @@
         <v>182</v>
       </c>
       <c r="K213" s="9"/>
-      <c r="L213" s="25" t="s">
-        <v>405</v>
+      <c r="L213" s="9" t="s">
+        <v>404</v>
       </c>
       <c r="M213" s="9" t="s">
         <v>54</v>
@@ -15744,7 +15622,7 @@
         <v>26</v>
       </c>
       <c r="H214" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I214" s="9" t="s">
         <v>182</v>
@@ -15820,7 +15698,7 @@
         <v>26</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I215" s="9" t="s">
         <v>182</v>
@@ -15891,7 +15769,7 @@
         <v>26</v>
       </c>
       <c r="H216" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I216" s="9" t="s">
         <v>182</v>
@@ -15957,7 +15835,7 @@
         <v>26</v>
       </c>
       <c r="H217" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I217" s="9" t="s">
         <v>182</v>
@@ -15967,7 +15845,7 @@
       </c>
       <c r="K217" s="9"/>
       <c r="L217" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M217" s="9" t="s">
         <v>191</v>
@@ -16035,7 +15913,7 @@
         <v>26</v>
       </c>
       <c r="H218" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I218" s="9" t="s">
         <v>182</v>
@@ -16096,7 +15974,7 @@
         <v>26</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I219" s="9" t="s">
         <v>163</v>
@@ -16108,7 +15986,7 @@
         <v>182</v>
       </c>
       <c r="L219" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M219" s="9" t="s">
         <v>191</v>
@@ -16167,7 +16045,7 @@
         <v>277</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>25</v>
@@ -16176,7 +16054,7 @@
         <v>26</v>
       </c>
       <c r="H220" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I220" s="9" t="s">
         <v>163</v>
@@ -16186,7 +16064,7 @@
       </c>
       <c r="K220" s="9"/>
       <c r="L220" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M220" s="9" t="s">
         <v>191</v>
@@ -16240,7 +16118,7 @@
         <v>277</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>55</v>
@@ -16249,7 +16127,7 @@
         <v>26</v>
       </c>
       <c r="H221" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I221" s="9" t="s">
         <v>182</v>
@@ -16294,19 +16172,19 @@
     </row>
     <row r="222" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A222" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B222" s="17">
         <v>46086</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D222" s="9" t="s">
         <v>277</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>34</v>
@@ -16315,7 +16193,7 @@
         <v>26</v>
       </c>
       <c r="H222" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I222" s="9" t="s">
         <v>182</v>
@@ -16370,13 +16248,13 @@
     </row>
     <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B223" s="17">
         <v>46087</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D223" s="9" t="s">
         <v>277</v>
@@ -16391,7 +16269,7 @@
         <v>26</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I223" s="9" t="s">
         <v>182</v>
@@ -16446,13 +16324,13 @@
     </row>
     <row r="224" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A224" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B224" s="17">
         <v>46104</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D224" s="9" t="s">
         <v>277</v>
@@ -16467,7 +16345,7 @@
         <v>26</v>
       </c>
       <c r="H224" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I224" s="9" t="s">
         <v>182</v>
@@ -16522,13 +16400,13 @@
     </row>
     <row r="225" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B225" s="17">
         <v>46168</v>
       </c>
       <c r="C225" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D225" s="9" t="s">
         <v>277</v>
@@ -16543,7 +16421,7 @@
         <v>215</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I225" s="9" t="s">
         <v>231</v>
@@ -16593,7 +16471,7 @@
     </row>
     <row r="226" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B226" s="17">
         <v>46142</v>
@@ -16611,19 +16489,16 @@
         <v>34</v>
       </c>
       <c r="G226" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H226" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="H226" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="I226" s="9" t="s">
         <v>431</v>
-      </c>
-      <c r="I226" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="J226" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="K226" s="9" t="s">
-        <v>432</v>
       </c>
       <c r="L226" s="9" t="s">
         <v>177</v>
@@ -16673,7 +16548,7 @@
     </row>
     <row r="227" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B227" s="17">
         <v>46142</v>
@@ -16685,19 +16560,19 @@
         <v>277</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>403</v>
+        <v>69</v>
       </c>
       <c r="F227" s="9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="H227" s="9" t="s">
-        <v>434</v>
+        <v>59</v>
+      </c>
+      <c r="H227" s="25" t="s">
+        <v>430</v>
       </c>
       <c r="I227" s="9" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="J227" s="9"/>
       <c r="K227" s="9"/>
@@ -16716,10 +16591,10 @@
       </c>
       <c r="P227" s="9" t="str">
         <f>_xlfn.XLOOKUP(Q227,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
-        <v>Development</v>
+        <v>Legal</v>
       </c>
       <c r="Q227" s="9" t="s">
-        <v>199</v>
+        <v>39</v>
       </c>
       <c r="R227" s="9" t="str">
         <f>_xlfn.XLOOKUP(S227,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
@@ -16730,13 +16605,18 @@
       </c>
       <c r="T227" s="9" t="str">
         <f>_xlfn.XLOOKUP(U227,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
-        <v>Legal</v>
+        <v>Economic</v>
       </c>
       <c r="U227" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="V227" s="9"/>
-      <c r="W227" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="V227" s="9" t="str">
+        <f>_xlfn.XLOOKUP(W227,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
+        <v>Regulatory</v>
+      </c>
+      <c r="W227" s="9" t="s">
+        <v>158</v>
+      </c>
       <c r="X227" s="9" t="s">
         <v>31</v>
       </c>
@@ -16744,7 +16624,7 @@
     </row>
     <row r="228" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A228" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B228" s="17">
         <v>46142</v>
@@ -16756,23 +16636,21 @@
         <v>277</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>58</v>
+        <v>402</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>25</v>
       </c>
       <c r="G228" s="9" t="s">
-        <v>433</v>
+        <v>26</v>
       </c>
       <c r="H228" s="9" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I228" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="J228" s="9" t="s">
         <v>182</v>
       </c>
+      <c r="J228" s="9"/>
       <c r="K228" s="9"/>
       <c r="L228" s="9" t="s">
         <v>177</v>
@@ -16789,24 +16667,24 @@
       </c>
       <c r="P228" s="9" t="str">
         <f>_xlfn.XLOOKUP(Q228,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
-        <v>Legal</v>
+        <v>Development</v>
       </c>
       <c r="Q228" s="9" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="R228" s="9" t="str">
         <f>_xlfn.XLOOKUP(S228,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
         <v>Institutional</v>
       </c>
       <c r="S228" s="9" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="T228" s="9" t="str">
         <f>_xlfn.XLOOKUP(U228,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
-        <v>Institutional</v>
+        <v>Legal</v>
       </c>
       <c r="U228" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V228" s="9"/>
       <c r="W228" s="9"/>
@@ -16817,7 +16695,7 @@
     </row>
     <row r="229" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A229" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B229" s="17">
         <v>46142</v>
@@ -16829,19 +16707,23 @@
         <v>277</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F229" s="9" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G229" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H229" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="H229" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="I229" s="9"/>
-      <c r="J229" s="9"/>
+      <c r="I229" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="J229" s="9" t="s">
+        <v>182</v>
+      </c>
       <c r="K229" s="9"/>
       <c r="L229" s="9" t="s">
         <v>177</v>
@@ -16851,17 +16733,32 @@
       </c>
       <c r="N229" s="9" t="str">
         <f>_xlfn.XLOOKUP(O229,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
-        <v>Institutional</v>
+        <v>Political Economy</v>
       </c>
       <c r="O229" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P229" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Q229,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
+        <v>Legal</v>
+      </c>
+      <c r="Q229" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="R229" s="9" t="str">
+        <f>_xlfn.XLOOKUP(S229,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
+        <v>Institutional</v>
+      </c>
+      <c r="S229" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="T229" s="9" t="str">
+        <f>_xlfn.XLOOKUP(U229,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
+        <v>Institutional</v>
+      </c>
+      <c r="U229" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P229" s="9"/>
-      <c r="Q229" s="9"/>
-      <c r="R229" s="9"/>
-      <c r="S229" s="9"/>
-      <c r="T229" s="9"/>
-      <c r="U229" s="9"/>
       <c r="V229" s="9"/>
       <c r="W229" s="9"/>
       <c r="X229" s="9" t="s">
@@ -16869,8 +16766,62 @@
       </c>
       <c r="Y229" s="9"/>
     </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A230" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="B230" s="17">
+        <v>46142</v>
+      </c>
+      <c r="C230" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E230" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F230" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G230" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H230" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="I230" s="9"/>
+      <c r="J230" s="9"/>
+      <c r="K230" s="9"/>
+      <c r="L230" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="M230" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N230" s="9" t="str">
+        <f>_xlfn.XLOOKUP(O230,'[1]Governance Dimension_Topics'!$C$3:$C$16,'[1]Governance Dimension_Topics'!$B$3:$B$16,"None",0)</f>
+        <v>Institutional</v>
+      </c>
+      <c r="O230" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P230" s="9"/>
+      <c r="Q230" s="9"/>
+      <c r="R230" s="9"/>
+      <c r="S230" s="9"/>
+      <c r="T230" s="9"/>
+      <c r="U230" s="9"/>
+      <c r="V230" s="9"/>
+      <c r="W230" s="9"/>
+      <c r="X230" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y230" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y225" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Y230" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16938,7 +16889,7 @@
         <v>216</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="94.5" x14ac:dyDescent="0.25">
@@ -16949,7 +16900,7 @@
         <v>231</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -17127,7 +17078,7 @@
         <v>112</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>152</v>
